--- a/구성종목(PDF)TIME바이오액티브_2026-03-25.xlsx
+++ b/구성종목(PDF)TIME바이오액티브_2026-03-25.xlsx
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="5">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="97">
   <si>
     <t>종목코드</t>
   </si>
@@ -30,6 +30,282 @@
   </si>
   <si>
     <t>비중(%)</t>
+  </si>
+  <si>
+    <t>000250</t>
+  </si>
+  <si>
+    <t>삼천당제약</t>
+  </si>
+  <si>
+    <t>122,650,000</t>
+  </si>
+  <si>
+    <t>리가켐바이오</t>
+  </si>
+  <si>
+    <t>85,400,000</t>
+  </si>
+  <si>
+    <t>에이비엘바이오</t>
+  </si>
+  <si>
+    <t>77,362,700</t>
+  </si>
+  <si>
+    <t>올릭스</t>
+  </si>
+  <si>
+    <t>74,852,400</t>
+  </si>
+  <si>
+    <t>068270</t>
+  </si>
+  <si>
+    <t>셀트리온</t>
+  </si>
+  <si>
+    <t>62,678,000</t>
+  </si>
+  <si>
+    <t>에스티팜</t>
+  </si>
+  <si>
+    <t>48,169,000</t>
+  </si>
+  <si>
+    <t>알지노믹스</t>
+  </si>
+  <si>
+    <t>43,900,000</t>
+  </si>
+  <si>
+    <t>현금</t>
+  </si>
+  <si>
+    <t>42,254,971</t>
+  </si>
+  <si>
+    <t>한미약품</t>
+  </si>
+  <si>
+    <t>37,870,000</t>
+  </si>
+  <si>
+    <t>에이프릴바이오</t>
+  </si>
+  <si>
+    <t>37,377,600</t>
+  </si>
+  <si>
+    <t>알테오젠</t>
+  </si>
+  <si>
+    <t>36,208,500</t>
+  </si>
+  <si>
+    <t>씨어스테크놀로지</t>
+  </si>
+  <si>
+    <t>31,380,000</t>
+  </si>
+  <si>
+    <t>보로노이</t>
+  </si>
+  <si>
+    <t>24,300,000</t>
+  </si>
+  <si>
+    <t>068760</t>
+  </si>
+  <si>
+    <t>셀트리온제약</t>
+  </si>
+  <si>
+    <t>23,480,000</t>
+  </si>
+  <si>
+    <t>오름테라퓨틱</t>
+  </si>
+  <si>
+    <t>22,420,000</t>
+  </si>
+  <si>
+    <t>인벤티지랩</t>
+  </si>
+  <si>
+    <t>19,470,000</t>
+  </si>
+  <si>
+    <t>087010</t>
+  </si>
+  <si>
+    <t>펩트론</t>
+  </si>
+  <si>
+    <t>18,990,000</t>
+  </si>
+  <si>
+    <t>039200</t>
+  </si>
+  <si>
+    <t>오스코텍</t>
+  </si>
+  <si>
+    <t>16,163,700</t>
+  </si>
+  <si>
+    <t>리브스메드</t>
+  </si>
+  <si>
+    <t>15,858,900</t>
+  </si>
+  <si>
+    <t>삼성바이오로직스</t>
+  </si>
+  <si>
+    <t>15,850,000</t>
+  </si>
+  <si>
+    <t>코오롱티슈진</t>
+  </si>
+  <si>
+    <t>15,345,000</t>
+  </si>
+  <si>
+    <t>휴젤</t>
+  </si>
+  <si>
+    <t>12,900,000</t>
+  </si>
+  <si>
+    <t>일동제약</t>
+  </si>
+  <si>
+    <t>12,448,800</t>
+  </si>
+  <si>
+    <t>로킷헬스케어</t>
+  </si>
+  <si>
+    <t>12,270,600</t>
+  </si>
+  <si>
+    <t>지투지바이오</t>
+  </si>
+  <si>
+    <t>11,944,100</t>
+  </si>
+  <si>
+    <t>0009K0</t>
+  </si>
+  <si>
+    <t>에임드바이오</t>
+  </si>
+  <si>
+    <t>10,860,500</t>
+  </si>
+  <si>
+    <t>0126Z0</t>
+  </si>
+  <si>
+    <t>삼성에피스홀딩스</t>
+  </si>
+  <si>
+    <t>10,800,000</t>
+  </si>
+  <si>
+    <t>앱클론</t>
+  </si>
+  <si>
+    <t>10,035,000</t>
+  </si>
+  <si>
+    <t>케어젠</t>
+  </si>
+  <si>
+    <t>9,996,000</t>
+  </si>
+  <si>
+    <t>파마리서치</t>
+  </si>
+  <si>
+    <t>9,675,000</t>
+  </si>
+  <si>
+    <t>그래피</t>
+  </si>
+  <si>
+    <t>9,457,050</t>
+  </si>
+  <si>
+    <t>078160</t>
+  </si>
+  <si>
+    <t>메디포스트</t>
+  </si>
+  <si>
+    <t>8,640,000</t>
+  </si>
+  <si>
+    <t>디앤디파마텍</t>
+  </si>
+  <si>
+    <t>7,830,900</t>
+  </si>
+  <si>
+    <t>프로티나</t>
+  </si>
+  <si>
+    <t>7,352,800</t>
+  </si>
+  <si>
+    <t>토모큐브</t>
+  </si>
+  <si>
+    <t>5,860,000</t>
+  </si>
+  <si>
+    <t>009420</t>
+  </si>
+  <si>
+    <t>한올바이오파마</t>
+  </si>
+  <si>
+    <t>5,674,200</t>
+  </si>
+  <si>
+    <t>098460</t>
+  </si>
+  <si>
+    <t>고영</t>
+  </si>
+  <si>
+    <t>5,645,400</t>
+  </si>
+  <si>
+    <t>HK이노엔</t>
+  </si>
+  <si>
+    <t>5,406,000</t>
+  </si>
+  <si>
+    <t>001060</t>
+  </si>
+  <si>
+    <t>JW중외제약</t>
+  </si>
+  <si>
+    <t>3,233,400</t>
+  </si>
+  <si>
+    <t>085660</t>
+  </si>
+  <si>
+    <t>차바이오텍</t>
+  </si>
+  <si>
+    <t>1,948,320</t>
   </si>
 </sst>
 </file>
@@ -98,9 +374,12 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf xfId="0" fontId="0" numFmtId="0" fillId="0" borderId="0" applyFont="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0"/>
     <xf xfId="0" fontId="1" numFmtId="0" fillId="2" borderId="1" applyFont="1" applyNumberFormat="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" shrinkToFit="false"/>
+    </xf>
+    <xf xfId="0" fontId="0" numFmtId="0" fillId="0" borderId="1" applyFont="0" applyNumberFormat="0" applyFill="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" shrinkToFit="false"/>
     </xf>
   </cellXfs>
@@ -402,7 +681,7 @@
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
   </sheetPr>
-  <dimension ref="A1:E1"/>
+  <dimension ref="A1:E41"/>
   <sheetFormatPr defaultRowHeight="14.4" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col min="1" max="1" width="30" customWidth="true" style="0"/>
@@ -429,6 +708,684 @@
         <v>4</v>
       </c>
     </row>
+    <row r="2" spans="1:5" customHeight="1" ht="30">
+      <c r="A2" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="B2" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="C2" s="2">
+        <v>110</v>
+      </c>
+      <c r="D2" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="E2" s="2">
+        <v>11.86</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" customHeight="1" ht="30">
+      <c r="A3" s="2">
+        <v>141080</v>
+      </c>
+      <c r="B3" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="C3" s="2">
+        <v>400</v>
+      </c>
+      <c r="D3" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="E3" s="2">
+        <v>8.26</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" customHeight="1" ht="30">
+      <c r="A4" s="2">
+        <v>298380</v>
+      </c>
+      <c r="B4" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="C4" s="2">
+        <v>449</v>
+      </c>
+      <c r="D4" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="E4" s="2">
+        <v>7.48</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" customHeight="1" ht="30">
+      <c r="A5" s="2">
+        <v>226950</v>
+      </c>
+      <c r="B5" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="C5" s="2">
+        <v>399</v>
+      </c>
+      <c r="D5" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="E5" s="2">
+        <v>7.24</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5" customHeight="1" ht="30">
+      <c r="A6" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="B6" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="C6" s="2">
+        <v>308</v>
+      </c>
+      <c r="D6" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="E6" s="2">
+        <v>6.06</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5" customHeight="1" ht="30">
+      <c r="A7" s="2">
+        <v>237690</v>
+      </c>
+      <c r="B7" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="C7" s="2">
+        <v>302</v>
+      </c>
+      <c r="D7" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="E7" s="2">
+        <v>4.66</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5" customHeight="1" ht="30">
+      <c r="A8" s="2">
+        <v>476830</v>
+      </c>
+      <c r="B8" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="C8" s="2">
+        <v>200</v>
+      </c>
+      <c r="D8" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="E8" s="2">
+        <v>4.25</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5" customHeight="1" ht="30">
+      <c r="A9" s="2"/>
+      <c r="B9" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="C9" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="D9" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="E9" s="2">
+        <v>4.09</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5" customHeight="1" ht="30">
+      <c r="A10" s="2">
+        <v>128940</v>
+      </c>
+      <c r="B10" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="C10" s="2">
+        <v>70</v>
+      </c>
+      <c r="D10" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="E10" s="2">
+        <v>3.66</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5" customHeight="1" ht="30">
+      <c r="A11" s="2">
+        <v>397030</v>
+      </c>
+      <c r="B11" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="C11" s="2">
+        <v>599</v>
+      </c>
+      <c r="D11" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="E11" s="2">
+        <v>3.62</v>
+      </c>
+    </row>
+    <row r="12" spans="1:5" customHeight="1" ht="30">
+      <c r="A12" s="2">
+        <v>196170</v>
+      </c>
+      <c r="B12" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="C12" s="2">
+        <v>101</v>
+      </c>
+      <c r="D12" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="E12" s="2">
+        <v>3.5</v>
+      </c>
+    </row>
+    <row r="13" spans="1:5" customHeight="1" ht="30">
+      <c r="A13" s="2">
+        <v>458870</v>
+      </c>
+      <c r="B13" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="C13" s="2">
+        <v>600</v>
+      </c>
+      <c r="D13" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="E13" s="2">
+        <v>3.04</v>
+      </c>
+    </row>
+    <row r="14" spans="1:5" customHeight="1" ht="30">
+      <c r="A14" s="2">
+        <v>310210</v>
+      </c>
+      <c r="B14" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="C14" s="2">
+        <v>81</v>
+      </c>
+      <c r="D14" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="E14" s="2">
+        <v>2.35</v>
+      </c>
+    </row>
+    <row r="15" spans="1:5" customHeight="1" ht="30">
+      <c r="A15" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="B15" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="C15" s="2">
+        <v>400</v>
+      </c>
+      <c r="D15" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="E15" s="2">
+        <v>2.27</v>
+      </c>
+    </row>
+    <row r="16" spans="1:5" customHeight="1" ht="30">
+      <c r="A16" s="2">
+        <v>475830</v>
+      </c>
+      <c r="B16" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="C16" s="2">
+        <v>200</v>
+      </c>
+      <c r="D16" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="E16" s="2">
+        <v>2.17</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5" customHeight="1" ht="30">
+      <c r="A17" s="2">
+        <v>389470</v>
+      </c>
+      <c r="B17" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="C17" s="2">
+        <v>275</v>
+      </c>
+      <c r="D17" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="E17" s="2">
+        <v>1.88</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5" customHeight="1" ht="30">
+      <c r="A18" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="B18" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="C18" s="2">
+        <v>60</v>
+      </c>
+      <c r="D18" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="E18" s="2">
+        <v>1.84</v>
+      </c>
+    </row>
+    <row r="19" spans="1:5" customHeight="1" ht="30">
+      <c r="A19" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="B19" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="C19" s="2">
+        <v>301</v>
+      </c>
+      <c r="D19" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="E19" s="2">
+        <v>1.56</v>
+      </c>
+    </row>
+    <row r="20" spans="1:5" customHeight="1" ht="30">
+      <c r="A20" s="2">
+        <v>491000</v>
+      </c>
+      <c r="B20" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="C20" s="2">
+        <v>201</v>
+      </c>
+      <c r="D20" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="E20" s="2">
+        <v>1.53</v>
+      </c>
+    </row>
+    <row r="21" spans="1:5" customHeight="1" ht="30">
+      <c r="A21" s="2">
+        <v>207940</v>
+      </c>
+      <c r="B21" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="C21" s="2">
+        <v>10</v>
+      </c>
+      <c r="D21" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="E21" s="2">
+        <v>1.53</v>
+      </c>
+    </row>
+    <row r="22" spans="1:5" customHeight="1" ht="30">
+      <c r="A22" s="2">
+        <v>950160</v>
+      </c>
+      <c r="B22" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="C22" s="2">
+        <v>150</v>
+      </c>
+      <c r="D22" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="E22" s="2">
+        <v>1.48</v>
+      </c>
+    </row>
+    <row r="23" spans="1:5" customHeight="1" ht="30">
+      <c r="A23" s="2">
+        <v>145020</v>
+      </c>
+      <c r="B23" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="C23" s="2">
+        <v>50</v>
+      </c>
+      <c r="D23" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="E23" s="2">
+        <v>1.25</v>
+      </c>
+    </row>
+    <row r="24" spans="1:5" customHeight="1" ht="30">
+      <c r="A24" s="2">
+        <v>249420</v>
+      </c>
+      <c r="B24" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="C24" s="2">
+        <v>399</v>
+      </c>
+      <c r="D24" s="2" t="s">
+        <v>55</v>
+      </c>
+      <c r="E24" s="2">
+        <v>1.2</v>
+      </c>
+    </row>
+    <row r="25" spans="1:5" customHeight="1" ht="30">
+      <c r="A25" s="2">
+        <v>376900</v>
+      </c>
+      <c r="B25" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="C25" s="2">
+        <v>102</v>
+      </c>
+      <c r="D25" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="E25" s="2">
+        <v>1.19</v>
+      </c>
+    </row>
+    <row r="26" spans="1:5" customHeight="1" ht="30">
+      <c r="A26" s="2">
+        <v>456160</v>
+      </c>
+      <c r="B26" s="2" t="s">
+        <v>58</v>
+      </c>
+      <c r="C26" s="2">
+        <v>151</v>
+      </c>
+      <c r="D26" s="2" t="s">
+        <v>59</v>
+      </c>
+      <c r="E26" s="2">
+        <v>1.16</v>
+      </c>
+    </row>
+    <row r="27" spans="1:5" customHeight="1" ht="30">
+      <c r="A27" s="2" t="s">
+        <v>60</v>
+      </c>
+      <c r="B27" s="2" t="s">
+        <v>61</v>
+      </c>
+      <c r="C27" s="2">
+        <v>203</v>
+      </c>
+      <c r="D27" s="2" t="s">
+        <v>62</v>
+      </c>
+      <c r="E27" s="2">
+        <v>1.05</v>
+      </c>
+    </row>
+    <row r="28" spans="1:5" customHeight="1" ht="30">
+      <c r="A28" s="2" t="s">
+        <v>63</v>
+      </c>
+      <c r="B28" s="2" t="s">
+        <v>64</v>
+      </c>
+      <c r="C28" s="2">
+        <v>20</v>
+      </c>
+      <c r="D28" s="2" t="s">
+        <v>65</v>
+      </c>
+      <c r="E28" s="2">
+        <v>1.05</v>
+      </c>
+    </row>
+    <row r="29" spans="1:5" customHeight="1" ht="30">
+      <c r="A29" s="2">
+        <v>174900</v>
+      </c>
+      <c r="B29" s="2" t="s">
+        <v>66</v>
+      </c>
+      <c r="C29" s="2">
+        <v>150</v>
+      </c>
+      <c r="D29" s="2" t="s">
+        <v>67</v>
+      </c>
+      <c r="E29" s="2">
+        <v>0.97</v>
+      </c>
+    </row>
+    <row r="30" spans="1:5" customHeight="1" ht="30">
+      <c r="A30" s="2">
+        <v>214370</v>
+      </c>
+      <c r="B30" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="C30" s="2">
+        <v>102</v>
+      </c>
+      <c r="D30" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="E30" s="2">
+        <v>0.97</v>
+      </c>
+    </row>
+    <row r="31" spans="1:5" customHeight="1" ht="30">
+      <c r="A31" s="2">
+        <v>214450</v>
+      </c>
+      <c r="B31" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="C31" s="2">
+        <v>30</v>
+      </c>
+      <c r="D31" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="E31" s="2">
+        <v>0.94</v>
+      </c>
+    </row>
+    <row r="32" spans="1:5" customHeight="1" ht="30">
+      <c r="A32" s="2">
+        <v>318060</v>
+      </c>
+      <c r="B32" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="C32" s="2">
+        <v>201</v>
+      </c>
+      <c r="D32" s="2" t="s">
+        <v>73</v>
+      </c>
+      <c r="E32" s="2">
+        <v>0.92</v>
+      </c>
+    </row>
+    <row r="33" spans="1:5" customHeight="1" ht="30">
+      <c r="A33" s="2" t="s">
+        <v>74</v>
+      </c>
+      <c r="B33" s="2" t="s">
+        <v>75</v>
+      </c>
+      <c r="C33" s="2">
+        <v>400</v>
+      </c>
+      <c r="D33" s="2" t="s">
+        <v>76</v>
+      </c>
+      <c r="E33" s="2">
+        <v>0.84</v>
+      </c>
+    </row>
+    <row r="34" spans="1:5" customHeight="1" ht="30">
+      <c r="A34" s="2">
+        <v>347850</v>
+      </c>
+      <c r="B34" s="2" t="s">
+        <v>77</v>
+      </c>
+      <c r="C34" s="2">
+        <v>99</v>
+      </c>
+      <c r="D34" s="2" t="s">
+        <v>78</v>
+      </c>
+      <c r="E34" s="2">
+        <v>0.76</v>
+      </c>
+    </row>
+    <row r="35" spans="1:5" customHeight="1" ht="30">
+      <c r="A35" s="2">
+        <v>468530</v>
+      </c>
+      <c r="B35" s="2" t="s">
+        <v>79</v>
+      </c>
+      <c r="C35" s="2">
+        <v>101</v>
+      </c>
+      <c r="D35" s="2" t="s">
+        <v>80</v>
+      </c>
+      <c r="E35" s="2">
+        <v>0.71</v>
+      </c>
+    </row>
+    <row r="36" spans="1:5" customHeight="1" ht="30">
+      <c r="A36" s="2">
+        <v>475960</v>
+      </c>
+      <c r="B36" s="2" t="s">
+        <v>81</v>
+      </c>
+      <c r="C36" s="2">
+        <v>100</v>
+      </c>
+      <c r="D36" s="2" t="s">
+        <v>82</v>
+      </c>
+      <c r="E36" s="2">
+        <v>0.57</v>
+      </c>
+    </row>
+    <row r="37" spans="1:5" customHeight="1" ht="30">
+      <c r="A37" s="2" t="s">
+        <v>83</v>
+      </c>
+      <c r="B37" s="2" t="s">
+        <v>84</v>
+      </c>
+      <c r="C37" s="2">
+        <v>98</v>
+      </c>
+      <c r="D37" s="2" t="s">
+        <v>85</v>
+      </c>
+      <c r="E37" s="2">
+        <v>0.55</v>
+      </c>
+    </row>
+    <row r="38" spans="1:5" customHeight="1" ht="30">
+      <c r="A38" s="2" t="s">
+        <v>86</v>
+      </c>
+      <c r="B38" s="2" t="s">
+        <v>87</v>
+      </c>
+      <c r="C38" s="2">
+        <v>194</v>
+      </c>
+      <c r="D38" s="2" t="s">
+        <v>88</v>
+      </c>
+      <c r="E38" s="2">
+        <v>0.55</v>
+      </c>
+    </row>
+    <row r="39" spans="1:5" customHeight="1" ht="30">
+      <c r="A39" s="2">
+        <v>195940</v>
+      </c>
+      <c r="B39" s="2" t="s">
+        <v>89</v>
+      </c>
+      <c r="C39" s="2">
+        <v>102</v>
+      </c>
+      <c r="D39" s="2" t="s">
+        <v>90</v>
+      </c>
+      <c r="E39" s="2">
+        <v>0.52</v>
+      </c>
+    </row>
+    <row r="40" spans="1:5" customHeight="1" ht="30">
+      <c r="A40" s="2" t="s">
+        <v>91</v>
+      </c>
+      <c r="B40" s="2" t="s">
+        <v>92</v>
+      </c>
+      <c r="C40" s="2">
+        <v>102</v>
+      </c>
+      <c r="D40" s="2" t="s">
+        <v>93</v>
+      </c>
+      <c r="E40" s="2">
+        <v>0.31</v>
+      </c>
+    </row>
+    <row r="41" spans="1:5" customHeight="1" ht="30">
+      <c r="A41" s="2" t="s">
+        <v>94</v>
+      </c>
+      <c r="B41" s="2" t="s">
+        <v>95</v>
+      </c>
+      <c r="C41" s="2">
+        <v>99</v>
+      </c>
+      <c r="D41" s="2" t="s">
+        <v>96</v>
+      </c>
+      <c r="E41" s="2">
+        <v>0.19</v>
+      </c>
+    </row>
   </sheetData>
   <printOptions gridLines="false" gridLinesSet="true"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
